--- a/salidas/empresas/PANW.xlsx
+++ b/salidas/empresas/PANW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B7" t="n">
@@ -602,7 +614,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B8" t="n">
@@ -627,7 +639,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B9" t="n">
@@ -652,7 +664,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +689,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B11" t="n">
@@ -702,7 +714,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B12" t="n">
@@ -727,7 +739,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B13" t="n">
@@ -752,7 +764,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B14" t="n">
@@ -777,7 +789,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B15" t="n">
@@ -802,7 +814,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B16" t="n">
@@ -829,7 +841,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B17" t="n">
@@ -856,7 +868,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B18" t="n">
@@ -883,7 +895,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B19" t="n">
@@ -910,7 +922,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B20" t="n">
@@ -937,7 +949,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B21" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B22" t="n">
@@ -991,7 +1003,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B23" t="n">
@@ -1018,7 +1030,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B24" t="n">
@@ -1045,7 +1057,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B25" t="n">
@@ -1072,7 +1084,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B26" t="n">
@@ -1099,7 +1111,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B27" t="n">
@@ -1126,7 +1138,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B28" t="n">
@@ -1153,7 +1165,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B29" t="n">
@@ -1180,7 +1192,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B30" t="n">
@@ -1207,7 +1219,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B31" t="n">
@@ -1234,7 +1246,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B32" t="n">
@@ -1261,7 +1273,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B33" t="n">
@@ -1288,7 +1300,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B34" t="n">
@@ -1315,7 +1327,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B35" t="n">
@@ -1342,7 +1354,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B36" t="n">
@@ -1369,7 +1381,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B37" t="n">
@@ -1396,7 +1408,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B38" t="n">
@@ -1423,7 +1435,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B39" t="n">
@@ -1450,7 +1462,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B40" t="n">
@@ -1477,7 +1489,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B41" t="n">
@@ -1504,7 +1516,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B42" t="n">
@@ -1531,7 +1543,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B43" t="n">
@@ -1558,7 +1570,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B44" t="n">
@@ -1585,7 +1597,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B45" t="n">
@@ -1612,7 +1624,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B46" t="n">
@@ -1639,7 +1651,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B47" t="n">
@@ -1666,7 +1678,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B48" t="n">
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B49" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B50" t="n">
@@ -1747,7 +1759,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B51" t="n">
@@ -1774,7 +1786,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B52" t="n">
@@ -1801,7 +1813,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B53" t="n">
@@ -1828,7 +1840,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B54" t="n">
@@ -1855,7 +1867,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B55" t="n">
@@ -1882,7 +1894,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B56" t="n">
@@ -1909,7 +1921,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B57" t="n">
@@ -1936,7 +1948,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B58" t="n">
@@ -1963,7 +1975,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B59" t="n">
@@ -1990,7 +2002,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B60" t="n">
@@ -2017,7 +2029,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B61" t="n">
@@ -2044,7 +2056,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B62" t="n">
@@ -2071,7 +2083,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B63" t="n">
@@ -2098,7 +2110,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B64" t="n">
@@ -2125,7 +2137,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B65" t="n">
@@ -2152,7 +2164,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B66" t="n">
@@ -2179,7 +2191,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B67" t="n">
@@ -2206,7 +2218,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B68" t="n">
@@ -2233,7 +2245,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B69" t="n">
@@ -2260,7 +2272,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B70" t="n">
@@ -2287,7 +2299,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B71" t="n">
@@ -2312,7 +2324,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B72" t="n">
@@ -2337,7 +2349,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B73" t="n">
@@ -2362,7 +2374,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B74" t="n">
@@ -2387,7 +2399,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B75" t="n">
@@ -2412,7 +2424,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B76" t="n">
@@ -2437,7 +2449,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B77" t="n">
@@ -2462,7 +2474,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B78" t="n">
@@ -2487,7 +2499,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B79" t="n">
@@ -2512,7 +2524,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B80" t="n">
@@ -2537,7 +2549,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B81" t="n">
@@ -2562,7 +2574,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B82" t="n">
@@ -2587,7 +2599,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B83" t="n">
@@ -2612,7 +2624,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B84" t="n">
@@ -2637,7 +2649,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B85" t="n">
@@ -2662,7 +2674,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B86" t="n">
@@ -2687,7 +2699,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B87" t="n">
@@ -2712,7 +2724,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B88" t="n">
@@ -2739,7 +2751,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B89" t="n">
@@ -2766,7 +2778,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B90" t="n">
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B91" t="n">
@@ -2820,7 +2832,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B92" t="n">
@@ -2847,7 +2859,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B93" t="n">
@@ -2874,7 +2886,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B94" t="n">
@@ -2901,7 +2913,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B95" t="n">
@@ -2928,7 +2940,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B96" t="n">
@@ -2955,7 +2967,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B97" t="n">
@@ -2982,7 +2994,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B98" t="n">
@@ -3009,7 +3021,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B99" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B100" t="n">
@@ -3063,7 +3075,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B101" t="n">
@@ -3090,7 +3102,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B102" t="n">
@@ -3117,7 +3129,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B103" t="n">
@@ -3144,7 +3156,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B104" t="n">
@@ -3171,7 +3183,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B105" t="n">
@@ -3198,7 +3210,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B106" t="n">
@@ -3225,7 +3237,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B107" t="n">
@@ -3252,7 +3264,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B108" t="n">
@@ -3279,7 +3291,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B109" t="n">
@@ -3306,7 +3318,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B110" t="n">
@@ -3333,7 +3345,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B111" t="n">
@@ -3360,7 +3372,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B112" t="n">
@@ -3387,7 +3399,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B113" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B114" t="n">
@@ -3437,7 +3449,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B115" t="n">
@@ -3462,7 +3474,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B116" t="n">
@@ -3487,7 +3499,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B117" t="n">
@@ -3512,7 +3524,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B118" t="n">
@@ -3537,7 +3549,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B119" t="n">
@@ -3562,7 +3574,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B120" t="n">
@@ -3589,7 +3601,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B121" t="n">
@@ -3616,7 +3628,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B122" t="n">
@@ -3643,7 +3655,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B123" t="n">
@@ -3670,7 +3682,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B124" t="n">
@@ -3697,7 +3709,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B125" t="n">
@@ -3724,7 +3736,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B126" t="n">
@@ -3751,7 +3763,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B127" t="n">
@@ -3778,7 +3790,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B128" t="n">
@@ -3805,7 +3817,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B129" t="n">
@@ -3834,7 +3846,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B130" t="n">
@@ -3863,7 +3875,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B131" t="n">
@@ -3892,7 +3904,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B132" t="n">
@@ -3921,7 +3933,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B133" t="n">
@@ -3950,7 +3962,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B134" t="n">
@@ -3979,7 +3991,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B135" t="n">
@@ -4008,7 +4020,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B136" t="n">
@@ -4037,7 +4049,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B137" t="n">
@@ -4066,7 +4078,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B138" t="n">
@@ -4095,7 +4107,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B139" t="n">
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B140" t="n">
@@ -4153,7 +4165,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B141" t="n">
@@ -4182,7 +4194,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B142" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B143" t="n">
@@ -4240,7 +4252,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B144" t="n">
@@ -4269,7 +4281,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B145" t="n">
@@ -4298,7 +4310,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B146" t="n">
@@ -4327,7 +4339,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B147" t="n">
@@ -4356,7 +4368,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B148" t="n">
@@ -4385,7 +4397,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B149" t="n">
@@ -4414,7 +4426,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B150" t="n">
@@ -4443,7 +4455,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B151" t="n">
@@ -4472,7 +4484,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B152" t="n">
@@ -4501,7 +4513,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B153" t="n">
@@ -4530,7 +4542,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B154" t="n">
@@ -4559,7 +4571,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B155" t="n">
@@ -4588,7 +4600,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B156" t="n">
@@ -4617,7 +4629,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B157" t="n">
@@ -4646,7 +4658,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B158" t="n">
@@ -4675,7 +4687,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B159" t="n">
@@ -4704,7 +4716,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B160" t="n">
@@ -4733,7 +4745,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B161" t="n">
@@ -4762,7 +4774,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B162" t="n">
@@ -4791,7 +4803,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B163" t="n">
@@ -4820,7 +4832,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B164" t="n">
@@ -4849,7 +4861,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B165" t="n">
@@ -4878,7 +4890,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B166" t="n">
@@ -4907,7 +4919,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B167" t="n">
@@ -4936,7 +4948,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B168" t="n">
@@ -4965,7 +4977,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B169" t="n">
@@ -4994,7 +5006,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B170" t="n">
@@ -5023,7 +5035,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B171" t="n">
@@ -5052,32 +5064,32 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B172" t="n">
-        <v>393.2999877929688</v>
+        <v>389.9200134277344</v>
       </c>
       <c r="C172" t="n">
-        <v>393.2999877929688</v>
+        <v>389.9200134277344</v>
       </c>
       <c r="D172" t="n">
-        <v>118516800</v>
+        <v>122484500</v>
       </c>
       <c r="E172" t="n">
         <v>0.3999999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>983.2499694824221</v>
+        <v>974.8000335693362</v>
       </c>
       <c r="G172" t="n">
         <v>818000000</v>
       </c>
       <c r="H172" t="n">
-        <v>321719390014.6484</v>
+        <v>318954570983.8867</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1448860635696821</v>
+        <v>0.1497365525672372</v>
       </c>
     </row>
   </sheetData>
@@ -5109,75 +5121,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5213,13 +5225,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5255,13 +5267,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41429</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5297,13 +5309,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5330,7 +5342,7 @@
       <c r="I5" t="n">
         <v>-0.03</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="K5" t="n">
@@ -5343,13 +5355,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5376,7 +5388,7 @@
       <c r="I6" t="n">
         <v>-0.03833333333333333</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="K6" t="n">
@@ -5389,13 +5401,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5422,7 +5434,7 @@
       <c r="I7" t="n">
         <v>-0.045</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="K7" t="n">
@@ -5435,13 +5447,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41429</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5468,7 +5480,7 @@
       <c r="I8" t="n">
         <v>-0.06166666666666666</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="K8" t="n">
@@ -5481,13 +5493,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5514,7 +5526,7 @@
       <c r="I9" t="n">
         <v>-0.06833333333333333</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="K9" t="n">
@@ -5527,13 +5539,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41613</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5560,7 +5572,7 @@
       <c r="I10" t="n">
         <v>-0.07833333333333334</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41613</v>
       </c>
       <c r="K10" t="n">
@@ -5573,13 +5585,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5606,7 +5618,7 @@
       <c r="I11" t="n">
         <v>-0.1633333333333333</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="K11" t="n">
@@ -5619,13 +5631,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41793</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -5652,7 +5664,7 @@
       <c r="I12" t="n">
         <v>-0.4733333333333333</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41793</v>
       </c>
       <c r="K12" t="n">
@@ -5665,13 +5677,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -5698,7 +5710,7 @@
       <c r="I13" t="n">
         <v>-0.505</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="K13" t="n">
@@ -5711,13 +5723,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41968</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -5744,7 +5756,7 @@
       <c r="I14" t="n">
         <v>-0.55</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41968</v>
       </c>
       <c r="K14" t="n">
@@ -5757,13 +5769,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42066</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -5790,7 +5802,7 @@
       <c r="I15" t="n">
         <v>-0.5466666666666666</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42066</v>
       </c>
       <c r="K15" t="n">
@@ -5803,13 +5815,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -5836,7 +5848,7 @@
       <c r="I16" t="n">
         <v>-0.3133333333333334</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="K16" t="n">
@@ -5849,13 +5861,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42264</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -5882,7 +5894,7 @@
       <c r="I17" t="n">
         <v>-0.3366666666666667</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42264</v>
       </c>
       <c r="K17" t="n">
@@ -5895,13 +5907,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -5928,7 +5940,7 @@
       <c r="I18" t="n">
         <v>-0.3483333333333333</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="K18" t="n">
@@ -5941,13 +5953,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -5974,7 +5986,7 @@
       <c r="I19" t="n">
         <v>-0.38</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K19" t="n">
@@ -5987,13 +5999,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6020,7 +6032,7 @@
       <c r="I20" t="n">
         <v>-0.42</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="K20" t="n">
@@ -6033,13 +6045,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42621</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6066,7 +6078,7 @@
       <c r="I21" t="n">
         <v>-0.43</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42621</v>
       </c>
       <c r="K21" t="n">
@@ -6079,13 +6091,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6112,7 +6124,7 @@
       <c r="I22" t="n">
         <v>-0.47</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="K22" t="n">
@@ -6125,13 +6137,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6158,7 +6170,7 @@
       <c r="I23" t="n">
         <v>-0.4616666666666667</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="K23" t="n">
@@ -6171,13 +6183,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6204,7 +6216,7 @@
       <c r="I24" t="n">
         <v>-0.4400000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="K24" t="n">
@@ -6217,13 +6229,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42985</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6250,7 +6262,7 @@
       <c r="I25" t="n">
         <v>-0.4083333333333333</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42985</v>
       </c>
       <c r="K25" t="n">
@@ -6263,13 +6275,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6296,7 +6308,7 @@
       <c r="I26" t="n">
         <v>-0.41</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K26" t="n">
@@ -6309,13 +6321,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6342,7 +6354,7 @@
       <c r="I27" t="n">
         <v>-0.345</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K27" t="n">
@@ -6355,13 +6367,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6388,7 +6400,7 @@
       <c r="I28" t="n">
         <v>-0.3066666666666666</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K28" t="n">
@@ -6401,13 +6413,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6434,7 +6446,7 @@
       <c r="I29" t="n">
         <v>-0.225</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K29" t="n">
@@ -6447,13 +6459,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6480,7 +6492,7 @@
       <c r="I30" t="n">
         <v>-0.1766666666666667</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K30" t="n">
@@ -6493,13 +6505,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6526,7 +6538,7 @@
       <c r="I31" t="n">
         <v>-0.135</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K31" t="n">
@@ -6539,13 +6551,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6572,7 +6584,7 @@
       <c r="I32" t="n">
         <v>-0.09666666666666666</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K32" t="n">
@@ -6585,13 +6597,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6618,7 +6630,7 @@
       <c r="I33" t="n">
         <v>-0.145</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="K33" t="n">
@@ -6631,13 +6643,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -6664,7 +6676,7 @@
       <c r="I34" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="K34" t="n">
@@ -6677,13 +6689,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -6710,7 +6722,7 @@
       <c r="I35" t="n">
         <v>-0.3</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K35" t="n">
@@ -6723,13 +6735,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -6756,7 +6768,7 @@
       <c r="I36" t="n">
         <v>-0.3933333333333333</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="K36" t="n">
@@ -6769,13 +6781,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -6802,7 +6814,7 @@
       <c r="I37" t="n">
         <v>-0.4583333333333333</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="K37" t="n">
@@ -6815,13 +6827,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -6848,7 +6860,7 @@
       <c r="I38" t="n">
         <v>-0.5166666666666666</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="K38" t="n">
@@ -6861,13 +6873,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -6894,7 +6906,7 @@
       <c r="I39" t="n">
         <v>-0.6383333333333333</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K39" t="n">
@@ -6907,13 +6919,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -6940,7 +6952,7 @@
       <c r="I40" t="n">
         <v>-0.76</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="K40" t="n">
@@ -6953,13 +6965,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -6986,7 +6998,7 @@
       <c r="I41" t="n">
         <v>-0.8645919778699862</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="K41" t="n">
@@ -6999,13 +7011,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7032,7 +7044,7 @@
       <c r="I42" t="n">
         <v>-0.8779253112033195</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="K42" t="n">
@@ -7045,13 +7057,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7078,7 +7090,7 @@
       <c r="I43" t="n">
         <v>-0.7912586445366528</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K43" t="n">
@@ -7091,13 +7103,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7124,7 +7136,7 @@
       <c r="I44" t="n">
         <v>-0.6645919778699861</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K44" t="n">
@@ -7137,13 +7149,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44810</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7170,7 +7182,7 @@
       <c r="I45" t="n">
         <v>-0.4527495769881557</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K45" t="n">
@@ -7183,13 +7195,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7216,7 +7228,7 @@
       <c r="I46" t="n">
         <v>-0.2477495769881557</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K46" t="n">
@@ -7229,13 +7241,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7262,7 +7274,7 @@
       <c r="I47" t="n">
         <v>0.03725042301184434</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K47" t="n">
@@ -7275,13 +7287,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45070</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7308,7 +7320,7 @@
       <c r="I48" t="n">
         <v>0.3155837563451777</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45070</v>
       </c>
       <c r="K48" t="n">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -7354,7 +7366,7 @@
       <c r="I49" t="n">
         <v>0.6400000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="K49" t="n">
@@ -7367,13 +7379,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -7400,7 +7412,7 @@
       <c r="I50" t="n">
         <v>0.8900000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="K50" t="n">
@@ -7413,13 +7425,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -7446,7 +7458,7 @@
       <c r="I51" t="n">
         <v>3.21</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K51" t="n">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -7492,7 +7504,7 @@
       <c r="I52" t="n">
         <v>3.45</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="K52" t="n">
@@ -7505,13 +7517,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -7538,7 +7550,7 @@
       <c r="I53" t="n">
         <v>3.640000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="K53" t="n">
@@ -7551,13 +7563,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -7584,7 +7596,7 @@
       <c r="I54" t="n">
         <v>3.855</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="K54" t="n">
@@ -7597,13 +7609,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -7630,7 +7642,7 @@
       <c r="I55" t="n">
         <v>1.79</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K55" t="n">
@@ -7643,13 +7655,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45798</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -7676,7 +7688,7 @@
       <c r="I56" t="n">
         <v>1.765000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45798</v>
       </c>
       <c r="K56" t="n">
@@ -7689,13 +7701,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -7722,7 +7734,7 @@
       <c r="I57" t="n">
         <v>1.6</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="K57" t="n">
@@ -7735,13 +7747,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -7768,7 +7780,7 @@
       <c r="I58" t="n">
         <v>1.575</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="K58" t="n">
@@ -7781,13 +7793,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -7814,7 +7826,7 @@
       <c r="I59" t="n">
         <v>1.805</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="K59" t="n">
@@ -7827,13 +7839,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -7860,7 +7872,7 @@
       <c r="I60" t="n">
         <v>1.215</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="K60" t="n">
@@ -7873,13 +7885,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -7906,7 +7918,7 @@
       <c r="I61" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="K61" t="n">
@@ -7943,52 +7955,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41253</v>
       </c>
       <c r="C2" t="n">
@@ -8017,10 +8029,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41337</v>
       </c>
       <c r="C3" t="n">
@@ -8049,10 +8061,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41409</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41429</v>
       </c>
       <c r="C4" t="n">
@@ -8081,10 +8093,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41527</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41542</v>
       </c>
       <c r="C5" t="n">
@@ -8113,10 +8125,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41593</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41613</v>
       </c>
       <c r="C6" t="n">
@@ -8145,10 +8157,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="C7" t="n">
@@ -8177,10 +8189,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41771</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41793</v>
       </c>
       <c r="C8" t="n">
@@ -8209,10 +8221,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41892</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="C9" t="n">
@@ -8241,10 +8253,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41960</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41968</v>
       </c>
       <c r="C10" t="n">
@@ -8273,10 +8285,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42053</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42066</v>
       </c>
       <c r="C11" t="n">
@@ -8305,10 +8317,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42142</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="C12" t="n">
@@ -8337,10 +8349,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42264</v>
       </c>
       <c r="C13" t="n">
@@ -8369,10 +8381,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42324</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="C14" t="n">
@@ -8401,10 +8413,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42417</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C15" t="n">
@@ -8433,10 +8445,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42507</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="C16" t="n">
@@ -8465,10 +8477,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42606</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42621</v>
       </c>
       <c r="C17" t="n">
@@ -8497,10 +8509,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42685</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="C18" t="n">
@@ -8529,10 +8541,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42782</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C19" t="n">
@@ -8561,10 +8573,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42872</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="C20" t="n">
@@ -8593,10 +8605,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42971</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42985</v>
       </c>
       <c r="C21" t="n">
@@ -8625,10 +8637,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43049</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="C22" t="n">
@@ -8657,10 +8669,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43146</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C23" t="n">
@@ -8689,10 +8701,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43238</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43256</v>
       </c>
       <c r="C24" t="n">
@@ -8721,10 +8733,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43342</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43356</v>
       </c>
       <c r="C25" t="n">
@@ -8753,10 +8765,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43424</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="C26" t="n">
@@ -8785,10 +8797,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43510</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C27" t="n">
@@ -8817,10 +8829,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43601</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="C28" t="n">
@@ -8849,10 +8861,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43700</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43717</v>
       </c>
       <c r="C29" t="n">
@@ -8881,10 +8893,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43782</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="C30" t="n">
@@ -8913,10 +8925,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43875</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="C31" t="n">
@@ -8945,10 +8957,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43965</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="C32" t="n">
@@ -8977,10 +8989,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44064</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="C33" t="n">
@@ -9009,10 +9021,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44148</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="C34" t="n">
@@ -9041,10 +9053,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C35" t="n">
@@ -9073,10 +9085,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44329</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="C36" t="n">
@@ -9105,10 +9117,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44431</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="C37" t="n">
@@ -9137,10 +9149,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44512</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="C38" t="n">
@@ -9169,10 +9181,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44606</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C39" t="n">
@@ -9201,10 +9213,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44693</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="C40" t="n">
@@ -9233,10 +9245,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44795</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44810</v>
       </c>
       <c r="C41" t="n">
@@ -9265,10 +9277,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44875</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="C42" t="n">
@@ -9297,10 +9309,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44967</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C43" t="n">
@@ -9329,10 +9341,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45058</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45070</v>
       </c>
       <c r="C44" t="n">
@@ -9361,10 +9373,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45156</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="C45" t="n">
@@ -9393,10 +9405,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45240</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="C46" t="n">
@@ -9425,10 +9437,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45334</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C47" t="n">
@@ -9457,10 +9469,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45422</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="C48" t="n">
@@ -9489,10 +9501,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45523</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="C49" t="n">
@@ -9521,10 +9533,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45609</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="C50" t="n">
@@ -9553,10 +9565,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45695</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C51" t="n">
@@ -9585,10 +9597,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45786</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45798</v>
       </c>
       <c r="C52" t="n">
@@ -9617,10 +9629,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45887</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="C53" t="n">
@@ -9649,10 +9661,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45972</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="C54" t="n">
@@ -9681,10 +9693,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46064</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="C55" t="n">
@@ -9713,10 +9725,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="C56" t="n">
@@ -9745,10 +9757,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46265</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="C57" t="n">
@@ -9795,12 +9807,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
